--- a/artfynd/A 29487-2022 artfynd.xlsx
+++ b/artfynd/A 29487-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 29487-2022 artfynd.xlsx
+++ b/artfynd/A 29487-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AY12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,12 +678,7 @@
         <v>1156904</v>
       </c>
       <c r="B2" t="n">
-        <v>89170</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Behöver inte valideras</t>
-        </is>
+        <v>91680</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>516970.8426033378</v>
+        <v>516971</v>
       </c>
       <c r="R2" t="n">
-        <v>6574626.540563273</v>
+        <v>6574627</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -748,19 +743,9 @@
           <t>2010-08-16</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2010-08-16</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -793,15 +778,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>111701910</v>
+        <v>111702281</v>
       </c>
       <c r="B3" t="n">
-        <v>90687</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91680</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -809,21 +789,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5964</v>
+        <v>3215</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus s.str.</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.:Fr.) P.Karst.</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -832,14 +812,14 @@
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Kyrkogården (Kyrkogården), Nrk</t>
+          <t>Kyrkogården, Kyrkogården, Nrk</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>516979</v>
+        <v>516918</v>
       </c>
       <c r="R3" t="n">
-        <v>6574636</v>
+        <v>6574656</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -878,7 +858,7 @@
         <v>0</v>
       </c>
       <c r="AE3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
@@ -899,15 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>111702281</v>
+        <v>128913753</v>
       </c>
       <c r="B4" t="n">
-        <v>89183</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93193</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -915,40 +890,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>3215</v>
+        <v>4363</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Zontaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Hydnellum concrescens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>(Pers.) Banker</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Kyrkogården (Kyrkogården), Nrk</t>
+          <t>Kyrkogården, Kyrkogården, Nrk</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>516918</v>
+        <v>516889</v>
       </c>
       <c r="R4" t="n">
-        <v>6574657</v>
+        <v>6574632</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -972,21 +944,20 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2023-08-26</t>
+          <t>2025-10-05</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2023-08-26</t>
+          <t>2025-10-05</t>
         </is>
       </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" t="b">
-        <v>1</v>
-      </c>
-      <c r="AF4" t="inlineStr"/>
+        <v>0</v>
+      </c>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1005,53 +976,56 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>111701829</v>
+        <v>111702271</v>
       </c>
       <c r="B5" t="n">
-        <v>90687</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93223</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5964</v>
+        <v>5448</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus s.str.</t>
+          <t>Phellodon melaleucus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
+          <t>(Sw. ex Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Myrövägen öster (Myrövägen öster), Nrk</t>
+          <t>Kyrkogården, Kyrkogården, Nrk</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>516895</v>
+        <v>516923</v>
       </c>
       <c r="R5" t="n">
-        <v>6574639</v>
+        <v>6574667</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1111,15 +1085,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>111702271</v>
+        <v>61907145</v>
       </c>
       <c r="B6" t="n">
-        <v>90709</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92404</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1127,45 +1096,36 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5448</v>
+        <v>5469</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Kärrvaxskinn</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellodon connatus</t>
+          <t>Phlebiodontia subochracea</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Schultz) nom.prov</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Bres.) Motato-Vásq. &amp; Gugliotta</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Kyrkogården (Kyrkogården), Nrk</t>
+          <t>Gudmunstorp S (Vivalla-Hovsta 694, södra), Nrk</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>516924</v>
+        <v>516864</v>
       </c>
       <c r="R6" t="n">
-        <v>6574667</v>
+        <v>6574610</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1192,12 +1152,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2023-08-26</t>
+          <t>2016-08-04</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2023-08-26</t>
+          <t>2016-08-04</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Område med högt naturvärde</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1210,18 +1175,656 @@
       <c r="AG6" t="b">
         <v>0</v>
       </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>Alsumpskog</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>Barklös alstam</t>
+        </is>
+      </c>
+      <c r="AS6" t="inlineStr">
+        <is>
+          <t>Karl-Henrik Larsson</t>
+        </is>
+      </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
+          <t>Anita Stridvall</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Anita Stridvall, Kurt-Anders Johansson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>Naturvärdesinventering av skogsbestånd runt Örebro stad 2016</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>61907243</v>
+      </c>
+      <c r="B7" t="n">
+        <v>92404</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>5469</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Kärrvaxskinn</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Phlebiodontia subochracea</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Bres.) Motato-Vásq. &amp; Gugliotta</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Gudmunstorp S (Vivalla-Hovsta 694, södra), Nrk</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>516882</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6574652</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Rinkaby</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2016-09-12</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2016-09-12</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Område med högt naturvärde</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>Alsumpskog</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>Alved</t>
+        </is>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Anita Stridvall</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Anita Stridvall, Kurt-Anders Johansson, Leif Andersson, Rolf-Göran Carlsson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>Naturvärdesinventering av skogsbestånd runt Örebro stad 2016</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>128914407</v>
+      </c>
+      <c r="B8" t="n">
+        <v>91409</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>5741</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Tjockfotad fingersvamp</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Ramaria flavescens</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Schaeff.) R. H. Petersen</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Kyrkogården, Kyrkogården, Nrk</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>516983</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6574622</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Rinkaby</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-10-05</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-10-05</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
           <t>Erik Göthlin</t>
         </is>
       </c>
-      <c r="AX6" t="inlineStr">
+      <c r="AX8" t="inlineStr">
         <is>
           <t>Erik Göthlin</t>
         </is>
       </c>
-      <c r="AY6" t="inlineStr"/>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>1721602</v>
+      </c>
+      <c r="B9" t="n">
+        <v>92928</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>5836</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Guldkremla</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Russula aurea</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Pers.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Myrö, Gudmundstorp, Nrk</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>516906</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6574578</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Rinkaby</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2010-08-16</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2010-08-16</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AR9" t="inlineStr"/>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Herbert Kaufmann</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Herbert Kaufmann</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>111701829</v>
+      </c>
+      <c r="B10" t="n">
+        <v>93233</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>5964</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Fjällig taggsvamp s.str.</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Sarcodon imbricatus</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Myrövägen öster, Myrövägen öster, Nrk</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>516895</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6574640</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Rinkaby</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2023-08-26</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2023-08-26</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF10" t="inlineStr"/>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Erik Göthlin</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Erik Göthlin</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>111701910</v>
+      </c>
+      <c r="B11" t="n">
+        <v>93233</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>5964</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Fjällig taggsvamp s.str.</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Sarcodon imbricatus</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Kyrkogården, Kyrkogården, Nrk</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>516979</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6574636</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Rinkaby</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2023-08-26</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2023-08-26</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF11" t="inlineStr"/>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Erik Göthlin</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Erik Göthlin</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>111701936</v>
+      </c>
+      <c r="B12" t="n">
+        <v>93233</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>5964</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Fjällig taggsvamp s.str.</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Sarcodon imbricatus</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Kyrkogården, Kyrkogården, Nrk</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>516986</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6574633</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Rinkaby</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2023-08-26</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2023-08-26</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF12" t="inlineStr"/>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Erik Göthlin</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Erik Göthlin</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 29487-2022 artfynd.xlsx
+++ b/artfynd/A 29487-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY12"/>
+  <dimension ref="A1:AZ12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -775,6 +780,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1156904</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -876,6 +886,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111702281</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -973,6 +988,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128913753</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1082,6 +1102,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111702271</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1206,6 +1231,11 @@
           <t>Naturvärdesinventering av skogsbestånd runt Örebro stad 2016</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61907145</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1322,6 +1352,11 @@
           <t>Naturvärdesinventering av skogsbestånd runt Örebro stad 2016</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61907243</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1419,6 +1454,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128914407</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1522,6 +1562,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1721602</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1623,6 +1668,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111701829</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1724,6 +1774,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111701910</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1825,8 +1880,26 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111701936</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>